--- a/mapping/input_01.xlsx
+++ b/mapping/input_01.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Practice\Python codes\Mappings\Episode 2\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\d\OneDrive - Indian Institute of Foreign Trade\Desktop\Practice\Python codes\Mappings\Python to Python\gen17\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A9AB22-F3AC-43C6-B4F4-40C8C8C0FAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80B8F9A-010F-4D52-A642-3433D36FD9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="input_01" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>a1</t>
   </si>
@@ -78,21 +78,6 @@
     <t>a4</t>
   </si>
   <si>
-    <t>id_01</t>
-  </si>
-  <si>
-    <t>id_02</t>
-  </si>
-  <si>
-    <t>id_03</t>
-  </si>
-  <si>
-    <t>id_04</t>
-  </si>
-  <si>
-    <t>id_05</t>
-  </si>
-  <si>
     <t>ida_01</t>
   </si>
   <si>
@@ -106,6 +91,21 @@
   </si>
   <si>
     <t>ida_05</t>
+  </si>
+  <si>
+    <t>idabc_02</t>
+  </si>
+  <si>
+    <t>idabc_03</t>
+  </si>
+  <si>
+    <t>idabc_04</t>
+  </si>
+  <si>
+    <t>idabc_05</t>
+  </si>
+  <si>
+    <t>act01</t>
   </si>
 </sst>
 </file>
@@ -135,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -143,12 +143,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -447,72 +459,86 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2">
-        <v>0.88996526380948404</v>
+        <v>0.18636929117410872</v>
       </c>
       <c r="D2">
         <v>0.60427026823619046</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
+      <c r="A3" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>0.18636929117410872</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="D3">
-        <v>0.35454075355423931</v>
+        <v>0.60427026823619046</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>9.468072963163876E-2</v>
+        <v>0.18636929117410872</v>
       </c>
       <c r="D4">
-        <v>0.760072283598067</v>
+        <v>0.35454075355423931</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>0.72201687147150162</v>
+        <v>9.468072963163876E-2</v>
       </c>
       <c r="D5">
-        <v>0.82428306831772313</v>
+        <v>9.468072963163876E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>0.82428306831772313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
+      <c r="C7">
         <v>0.83223147074281811</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>0.65713001019140704</v>
       </c>
     </row>
